--- a/backend/generated/Validation_Report.xlsx
+++ b/backend/generated/Validation_Report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24-05-2026 17:42</t>
+          <t>28-05-2026 10:30</t>
         </is>
       </c>
     </row>
